--- a/data/trans_bre/P16A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 13,29</t>
+          <t>3,05; 13,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 19,27</t>
+          <t>6,67; 18,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 10,23</t>
+          <t>-1,64; 10,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 18,44</t>
+          <t>7,91; 18,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,08; 129,8</t>
+          <t>20,02; 131,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,65; 183,34</t>
+          <t>41,72; 168,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 60,53</t>
+          <t>-6,93; 60,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,85; 117,55</t>
+          <t>36,34; 114,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 13,41</t>
+          <t>1,18; 12,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 22,0</t>
+          <t>8,04; 20,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 14,17</t>
+          <t>1,87; 14,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 16,27</t>
+          <t>5,5; 17,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 103,81</t>
+          <t>6,19; 97,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,57; 140,45</t>
+          <t>39,34; 134,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 98,69</t>
+          <t>9,12; 96,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,5; 91,63</t>
+          <t>23,35; 95,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 17,52</t>
+          <t>4,41; 19,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 13,67</t>
+          <t>0,44; 14,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 24,47</t>
+          <t>7,28; 24,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 45,62</t>
+          <t>17,45; 46,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,97; 151,63</t>
+          <t>31,2; 184,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 69,62</t>
+          <t>1,59; 78,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,73; 139,39</t>
+          <t>36,14; 139,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,69; 653,39</t>
+          <t>59,73; 616,68</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,09</t>
+          <t>1,76; 9,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,88</t>
+          <t>5,49; 13,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 13,03</t>
+          <t>4,85; 12,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 45,22</t>
+          <t>8,45; 42,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 58,87</t>
+          <t>9,47; 60,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,33; 73,39</t>
+          <t>24,75; 72,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,58; 71,11</t>
+          <t>22,94; 69,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 167,2</t>
+          <t>28,25; 165,62</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,78; 18,12</t>
+          <t>7,95; 18,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,34; 25,26</t>
+          <t>15,03; 25,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 22,44</t>
+          <t>12,59; 21,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 23,2</t>
+          <t>4,71; 24,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,5; 161,56</t>
+          <t>44,67; 158,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,78; 166,09</t>
+          <t>72,84; 168,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,12; 134,97</t>
+          <t>60,18; 133,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,9; 91,81</t>
+          <t>18,79; 97,94</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,18; 22,25</t>
+          <t>15,09; 22,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,61; 32,97</t>
+          <t>25,06; 33,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,89; 24,22</t>
+          <t>14,08; 24,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,04; 32,23</t>
+          <t>15,46; 32,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>174,85; 582,04</t>
+          <t>160,72; 540,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>228,06; 675,99</t>
+          <t>235,5; 716,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,12; 246,83</t>
+          <t>78,99; 245,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58,99; 419,89</t>
+          <t>67,26; 460,71</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,82</t>
+          <t>8,18; 11,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,63; 17,88</t>
+          <t>13,51; 17,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,12; 14,19</t>
+          <t>10,11; 14,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,62; 31,8</t>
+          <t>14,7; 32,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,07; 90,85</t>
+          <t>55,55; 91,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,76; 106,58</t>
+          <t>71,23; 105,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,47; 79,4</t>
+          <t>51,4; 80,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,09; 166,25</t>
+          <t>60,51; 163,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>11,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 13,9</t>
+          <t>2,93; 13,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 18,87</t>
+          <t>6,37; 18,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 10,04</t>
+          <t>-2,15; 9,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,91; 18,53</t>
+          <t>6,51; 16,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,02; 131,45</t>
+          <t>20,15; 139,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,72; 168,23</t>
+          <t>43,42; 180,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 60,54</t>
+          <t>-9,21; 57,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,34; 114,96</t>
+          <t>28,81; 98,23</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>11,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>59,89%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,51</t>
+          <t>1,01; 12,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 20,62</t>
+          <t>7,24; 21,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 14,2</t>
+          <t>1,62; 14,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 17,02</t>
+          <t>6,65; 17,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 97,5</t>
+          <t>5,57; 101,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,34; 134,25</t>
+          <t>34,09; 138,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 96,48</t>
+          <t>8,12; 93,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,35; 95,74</t>
+          <t>29,44; 99,08</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29,62</t>
+          <t>18,87</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>168,01%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 19,91</t>
+          <t>3,31; 18,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 14,61</t>
+          <t>0,75; 14,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 24,36</t>
+          <t>8,15; 24,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,45; 46,53</t>
+          <t>11,22; 26,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,2; 184,77</t>
+          <t>23,38; 161,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 78,22</t>
+          <t>3,31; 78,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,14; 139,16</t>
+          <t>37,68; 135,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,73; 616,68</t>
+          <t>36,4; 103,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,91</t>
+          <t>10,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 9,34</t>
+          <t>1,46; 9,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 13,73</t>
+          <t>5,51; 14,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 12,4</t>
+          <t>4,79; 12,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 42,65</t>
+          <t>5,9; 14,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 60,28</t>
+          <t>8,69; 62,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,75; 72,56</t>
+          <t>25,18; 78,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,94; 69,63</t>
+          <t>23,13; 70,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,25; 165,62</t>
+          <t>19,34; 54,23</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,43</t>
+          <t>22,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 18,04</t>
+          <t>7,82; 18,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,03; 25,67</t>
+          <t>15,17; 24,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,59; 21,52</t>
+          <t>12,27; 21,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 24,14</t>
+          <t>17,54; 27,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,67; 158,14</t>
+          <t>43,43; 159,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,84; 168,87</t>
+          <t>73,27; 162,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,18; 133,82</t>
+          <t>58,4; 133,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 97,94</t>
+          <t>61,39; 125,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,52</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>196,43%</t>
+          <t>238,77%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,09; 22,2</t>
+          <t>15,14; 22,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,06; 33,61</t>
+          <t>24,63; 33,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 24,54</t>
+          <t>14,53; 24,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,46; 32,25</t>
+          <t>19,93; 32,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>160,72; 540,36</t>
+          <t>171,94; 582,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>235,5; 716,82</t>
+          <t>230,83; 688,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,99; 245,26</t>
+          <t>84,25; 260,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67,26; 460,71</t>
+          <t>109,26; 498,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,58</t>
+          <t>15,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,91</t>
+          <t>8,14; 11,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,51; 17,74</t>
+          <t>13,57; 17,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,11; 14,48</t>
+          <t>10,22; 14,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 32,29</t>
+          <t>13,21; 17,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,55; 91,45</t>
+          <t>54,98; 90,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,23; 105,22</t>
+          <t>72,11; 105,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,4; 80,84</t>
+          <t>52,03; 80,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,51; 163,2</t>
+          <t>51,87; 75,46</t>
         </is>
       </c>
     </row>
